--- a/data/dividends_info_20260520.xlsx
+++ b/data/dividends_info_20260520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>54.65999984741211</v>
+        <v>55.27000045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.164654226584783</v>
+        <v>0.1628369807392644</v>
       </c>
       <c r="J2" t="n">
         <v>299</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>54.34999847412109</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.287948518219935</v>
+        <v>1.263537871335636</v>
       </c>
       <c r="J3" t="n">
         <v>278</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.199999809265137</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6535947495140209</v>
       </c>
       <c r="J4" t="n">
         <v>208</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>54.65999984741211</v>
+        <v>55.27000045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.164654226584783</v>
+        <v>0.1628369807392644</v>
       </c>
       <c r="J6" t="n">
         <v>208</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.009999990463257</v>
+        <v>2.035000085830688</v>
       </c>
       <c r="I7" t="n">
-        <v>3.830845789320295</v>
+        <v>3.783783624194224</v>
       </c>
       <c r="J7" t="n">
         <v>187</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.88500022888184</v>
+        <v>23.54000091552734</v>
       </c>
       <c r="I8" t="n">
-        <v>1.130416568610768</v>
+        <v>1.146983812655266</v>
       </c>
       <c r="J8" t="n">
         <v>187</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.570000171661377</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I9" t="n">
-        <v>3.590664162230099</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J9" t="n">
         <v>180</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8823529164271378</v>
       </c>
       <c r="J10" t="n">
         <v>152</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.400000095367432</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I12" t="n">
-        <v>0.925925909573486</v>
+        <v>0.9157509093529076</v>
       </c>
       <c r="J12" t="n">
         <v>138</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J13" t="n">
         <v>131</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.88500022888184</v>
+        <v>23.54000091552734</v>
       </c>
       <c r="I14" t="n">
-        <v>1.130416568610768</v>
+        <v>1.146983812655266</v>
       </c>
       <c r="J14" t="n">
         <v>124</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>54.65999984741211</v>
+        <v>55.27000045776367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.164654226584783</v>
+        <v>0.1628369807392644</v>
       </c>
       <c r="J15" t="n">
         <v>124</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.349999904632568</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="I16" t="n">
-        <v>6.896551875334814</v>
+        <v>6.833713191890466</v>
       </c>
       <c r="J16" t="n">
         <v>117</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J18" t="n">
         <v>75</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.829999923706055</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I19" t="n">
-        <v>4.288164721639967</v>
+        <v>4.266211506894081</v>
       </c>
       <c r="J19" t="n">
         <v>68</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.571999549865723</v>
+        <v>9.668999671936035</v>
       </c>
       <c r="I20" t="n">
-        <v>2.716255873660664</v>
+        <v>2.689006193211918</v>
       </c>
       <c r="J20" t="n">
         <v>61</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>4.026845740679177</v>
       </c>
       <c r="J21" t="n">
         <v>61</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.595999956130981</v>
+        <v>3.601999998092651</v>
       </c>
       <c r="I22" t="n">
-        <v>6.117908862176489</v>
+        <v>6.107717937715033</v>
       </c>
       <c r="J22" t="n">
         <v>61</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.965000152587891</v>
+        <v>6.005000114440918</v>
       </c>
       <c r="I24" t="n">
-        <v>4.023470140162142</v>
+        <v>3.99666936596461</v>
       </c>
       <c r="J24" t="n">
         <v>61</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.175000190734863</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="I26" t="n">
-        <v>2.874251365695823</v>
+        <v>2.857142986894471</v>
       </c>
       <c r="J26" t="n">
         <v>54</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.740000009536743</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I28" t="n">
-        <v>5.474452535690348</v>
+        <v>5.597014785954832</v>
       </c>
       <c r="J28" t="n">
         <v>54</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.200000047683716</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I29" t="n">
-        <v>3.863636279894303</v>
+        <v>3.899082449407415</v>
       </c>
       <c r="J29" t="n">
         <v>47</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>32.15000152587891</v>
+        <v>31.20000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>0.466562963859453</v>
+        <v>0.4807692190128909</v>
       </c>
       <c r="J31" t="n">
         <v>47</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.75</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6837606949074361</v>
       </c>
       <c r="J32" t="n">
         <v>40</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>22.71999931335449</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="I33" t="n">
-        <v>4.181338154537722</v>
+        <v>4.159369499357731</v>
       </c>
       <c r="J33" t="n">
         <v>33</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>32</v>
+        <v>32.70000076293945</v>
       </c>
       <c r="I34" t="n">
-        <v>0.609375</v>
+        <v>0.5963302613160892</v>
       </c>
       <c r="J34" t="n">
         <v>33</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.855000019073486</v>
+        <v>1.875</v>
       </c>
       <c r="I35" t="n">
-        <v>1.778975722948103</v>
+        <v>1.76</v>
       </c>
       <c r="J35" t="n">
         <v>33</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.144999980926514</v>
+        <v>5.210000038146973</v>
       </c>
       <c r="I36" t="n">
-        <v>5.6365403513136</v>
+        <v>5.566218769225643</v>
       </c>
       <c r="J36" t="n">
         <v>33</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.834000110626221</v>
+        <v>3.884000062942505</v>
       </c>
       <c r="I37" t="n">
-        <v>4.173187151365696</v>
+        <v>4.119464402860606</v>
       </c>
       <c r="J37" t="n">
         <v>33</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.70199990272522</v>
+        <v>2.716000080108643</v>
       </c>
       <c r="I38" t="n">
-        <v>5.129533863424974</v>
+        <v>5.10309263298902</v>
       </c>
       <c r="J38" t="n">
         <v>33</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>51.84000015258789</v>
+        <v>52.15999984741211</v>
       </c>
       <c r="I39" t="n">
-        <v>1.215277774200682</v>
+        <v>1.207822089422911</v>
       </c>
       <c r="J39" t="n">
         <v>33</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.230000019073486</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I40" t="n">
-        <v>2.676864234979516</v>
+        <v>2.65151504615341</v>
       </c>
       <c r="J40" t="n">
         <v>33</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.20000076293945</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="I41" t="n">
-        <v>4.06249983857076</v>
+        <v>4.041450936962817</v>
       </c>
       <c r="J41" t="n">
         <v>33</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24.47999954223633</v>
+        <v>24.78000068664551</v>
       </c>
       <c r="I42" t="n">
-        <v>3.47222228715103</v>
+        <v>3.43018553852617</v>
       </c>
       <c r="J42" t="n">
         <v>33</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>54.65999984741211</v>
+        <v>55.27000045776367</v>
       </c>
       <c r="I43" t="n">
-        <v>0.164654226584783</v>
+        <v>0.1628369807392644</v>
       </c>
       <c r="J43" t="n">
         <v>33</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.320000052452087</v>
+        <v>1.419999957084656</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7575757274724028</v>
+        <v>0.704225373395827</v>
       </c>
       <c r="J44" t="n">
         <v>33</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.354000091552734</v>
+        <v>6.35200023651123</v>
       </c>
       <c r="I45" t="n">
-        <v>2.85332070172658</v>
+        <v>2.854219037302447</v>
       </c>
       <c r="J45" t="n">
         <v>33</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.399999618530273</v>
+        <v>8.560000419616699</v>
       </c>
       <c r="I46" t="n">
-        <v>3.095238235802344</v>
+        <v>3.037383028675626</v>
       </c>
       <c r="J46" t="n">
         <v>33</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.944000244140625</v>
+        <v>9.965999603271484</v>
       </c>
       <c r="I47" t="n">
-        <v>2.785599288005034</v>
+        <v>2.779450241088417</v>
       </c>
       <c r="J47" t="n">
         <v>33</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.154999971389771</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="I48" t="n">
-        <v>1.168831197784008</v>
+        <v>1.173913067815886</v>
       </c>
       <c r="J48" t="n">
         <v>26</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.094000101089478</v>
+        <v>3.114000082015991</v>
       </c>
       <c r="I49" t="n">
-        <v>3.55526814499024</v>
+        <v>3.532434075235683</v>
       </c>
       <c r="J49" t="n">
         <v>26</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.099999904632568</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>1.142857194757788</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>26</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.140000104904175</v>
+        <v>3.214999914169312</v>
       </c>
       <c r="I51" t="n">
-        <v>5.095541231037086</v>
+        <v>4.976671983561799</v>
       </c>
       <c r="J51" t="n">
         <v>19</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9049999713897705</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="I52" t="n">
-        <v>2.762431026556669</v>
+        <v>2.808988809194278</v>
       </c>
       <c r="J52" t="n">
         <v>19</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>27.85000038146973</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="I53" t="n">
-        <v>3.985637288315981</v>
+        <v>3.901581617691721</v>
       </c>
       <c r="J53" t="n">
         <v>15</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.8659999966621399</v>
       </c>
       <c r="I54" t="n">
-        <v>3.409090927563422</v>
+        <v>3.464203246608575</v>
       </c>
       <c r="J54" t="n">
         <v>12</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5049999952316284</v>
       </c>
       <c r="I55" t="n">
-        <v>4.509804005899691</v>
+        <v>4.554455488549181</v>
       </c>
       <c r="J55" t="n">
         <v>12</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>3.022669967100398</v>
       </c>
       <c r="J56" t="n">
         <v>12</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8.880000114440918</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I57" t="n">
-        <v>2.252252223226372</v>
+        <v>2.207505416522502</v>
       </c>
       <c r="J57" t="n">
         <v>12</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.505000114440918</v>
+        <v>2.525000095367432</v>
       </c>
       <c r="I58" t="n">
-        <v>7.185628414239556</v>
+        <v>7.128712602040787</v>
       </c>
       <c r="J58" t="n">
         <v>5</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8.199999809265137</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I59" t="n">
-        <v>3.658536670464694</v>
+        <v>3.703703529277682</v>
       </c>
       <c r="J59" t="n">
         <v>5</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14.14000034332275</v>
+        <v>14.75</v>
       </c>
       <c r="I60" t="n">
-        <v>1.768033903323461</v>
+        <v>1.694915254237288</v>
       </c>
       <c r="J60" t="n">
         <v>5</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.450000047683716</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8695652053727246</v>
+        <v>0.862068960792339</v>
       </c>
       <c r="J61" t="n">
         <v>5</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.099999904632568</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="I62" t="n">
-        <v>3.658536670464694</v>
+        <v>3.57995221841372</v>
       </c>
       <c r="J62" t="n">
         <v>5</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13.89999961853027</v>
+        <v>14.55000019073486</v>
       </c>
       <c r="I63" t="n">
-        <v>4.17266198501757</v>
+        <v>3.986254243277137</v>
       </c>
       <c r="J63" t="n">
         <v>5</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.273000001907349</v>
+        <v>2.269000053405762</v>
       </c>
       <c r="I64" t="n">
-        <v>4.575450942047083</v>
+        <v>4.583516859944377</v>
       </c>
       <c r="J64" t="n">
         <v>-2</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.47000026702881</v>
+        <v>10.61499977111816</v>
       </c>
       <c r="I65" t="n">
-        <v>2.76981845848889</v>
+        <v>2.731983101771202</v>
       </c>
       <c r="J65" t="n">
         <v>-2</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.009999990463257</v>
+        <v>2.035000085830688</v>
       </c>
       <c r="I66" t="n">
-        <v>3.830845789320295</v>
+        <v>3.783783624194224</v>
       </c>
       <c r="J66" t="n">
         <v>-2</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>37.34999847412109</v>
+        <v>37.56999969482422</v>
       </c>
       <c r="I67" t="n">
-        <v>4.390897100400998</v>
+        <v>4.365185023480136</v>
       </c>
       <c r="J67" t="n">
         <v>-2</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>34.38000106811523</v>
+        <v>34.95999908447266</v>
       </c>
       <c r="I68" t="n">
-        <v>5.81733547953506</v>
+        <v>5.720823948443099</v>
       </c>
       <c r="J68" t="n">
         <v>-2</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3.296000003814697</v>
+        <v>3.203999996185303</v>
       </c>
       <c r="I69" t="n">
-        <v>3.033980579012828</v>
+        <v>3.121098630432599</v>
       </c>
       <c r="J69" t="n">
         <v>-2</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>32.06999969482422</v>
+        <v>32.54999923706055</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4629248562916575</v>
+        <v>0.4560983209823473</v>
       </c>
       <c r="J70" t="n">
         <v>-2</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.30999946594238</v>
+        <v>19.51000022888184</v>
       </c>
       <c r="I71" t="n">
-        <v>4.764370924104018</v>
+        <v>4.715530441860622</v>
       </c>
       <c r="J71" t="n">
         <v>-2</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>9.989999771118164</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I72" t="n">
-        <v>3.00300307180509</v>
+        <v>2.970296917516995</v>
       </c>
       <c r="J72" t="n">
         <v>-2</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>82.08000183105469</v>
+        <v>83.45999908447266</v>
       </c>
       <c r="I73" t="n">
-        <v>1.267056501948712</v>
+        <v>1.246105932672466</v>
       </c>
       <c r="J73" t="n">
         <v>-2</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>42.95000076293945</v>
+        <v>43.54000091552734</v>
       </c>
       <c r="I74" t="n">
-        <v>1.629802066508957</v>
+        <v>1.607717007994743</v>
       </c>
       <c r="J74" t="n">
         <v>-2</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>54.34999847412109</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="I75" t="n">
-        <v>4.047838200119797</v>
+        <v>3.971119024197713</v>
       </c>
       <c r="J75" t="n">
         <v>-2</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.526000022888184</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="I76" t="n">
-        <v>10.08679331094671</v>
+        <v>9.976798276305562</v>
       </c>
       <c r="J76" t="n">
         <v>-2</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.54399967193604</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="I77" t="n">
-        <v>4.851004988863473</v>
+        <v>4.81099642167315</v>
       </c>
       <c r="J77" t="n">
         <v>-2</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.640000343322754</v>
+        <v>8.760000228881836</v>
       </c>
       <c r="I79" t="n">
-        <v>3.472222084248513</v>
+        <v>3.424657444766908</v>
       </c>
       <c r="J79" t="n">
         <v>-2</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2.220000028610229</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I80" t="n">
-        <v>4.864864802168965</v>
+        <v>4.843049285931015</v>
       </c>
       <c r="J80" t="n">
         <v>-2</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>89.19999694824219</v>
+        <v>89</v>
       </c>
       <c r="I81" t="n">
-        <v>2.309417119369751</v>
+        <v>2.314606741573034</v>
       </c>
       <c r="J81" t="n">
         <v>-2</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>14.84000015258789</v>
+        <v>15.07999992370605</v>
       </c>
       <c r="I82" t="n">
-        <v>5.053908303829838</v>
+        <v>4.97347482622321</v>
       </c>
       <c r="J82" t="n">
         <v>-2</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13.30000019073486</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="I83" t="n">
-        <v>2.255639065396315</v>
+        <v>2.218934836113331</v>
       </c>
       <c r="J83" t="n">
         <v>-2</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>50.59999847412109</v>
+        <v>51</v>
       </c>
       <c r="I84" t="n">
-        <v>1.679841947890027</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J84" t="n">
         <v>-2</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>34.91999816894531</v>
+        <v>35.08000183105469</v>
       </c>
       <c r="I85" t="n">
-        <v>2.43413529372952</v>
+        <v>2.42303294080086</v>
       </c>
       <c r="J85" t="n">
         <v>-2</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>68.76000213623047</v>
+        <v>67.76000213623047</v>
       </c>
       <c r="I86" t="n">
-        <v>1.890634030848894</v>
+        <v>1.918535948960523</v>
       </c>
       <c r="J86" t="n">
         <v>-2</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>7.28000020980835</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I87" t="n">
-        <v>8.241758004232192</v>
+        <v>8.21917786744058</v>
       </c>
       <c r="J87" t="n">
         <v>-2</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.570000171661377</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I89" t="n">
-        <v>3.590664162230099</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J89" t="n">
         <v>-2</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.13999938964844</v>
+        <v>23.1200008392334</v>
       </c>
       <c r="I90" t="n">
-        <v>4.321521289440245</v>
+        <v>4.325259358568248</v>
       </c>
       <c r="J90" t="n">
         <v>-2</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.670000076293945</v>
+        <v>4.639999866485596</v>
       </c>
       <c r="I91" t="n">
-        <v>4.603854314508307</v>
+        <v>4.633620822986019</v>
       </c>
       <c r="J91" t="n">
         <v>-2</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>23.88500022888184</v>
+        <v>23.54000091552734</v>
       </c>
       <c r="I92" t="n">
-        <v>1.130416568610768</v>
+        <v>1.146983812655266</v>
       </c>
       <c r="J92" t="n">
         <v>-2</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.520000457763672</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I93" t="n">
-        <v>2.100840235116771</v>
+        <v>2.061855710646161</v>
       </c>
       <c r="J93" t="n">
         <v>-2</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.432</v>
+        <v>0.24</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>10.01000022888184</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="I94" t="n">
-        <v>4.315684217004822</v>
+        <v>2.923264298232194</v>
       </c>
       <c r="J94" t="n">
         <v>-2</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>25.71999931335449</v>
+        <v>21.1200008392334</v>
       </c>
       <c r="I95" t="n">
-        <v>1.710730994349368</v>
+        <v>3.740530154394989</v>
       </c>
       <c r="J95" t="n">
         <v>-2</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.03</v>
+        <v>0.093</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.019999980926514</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="I96" t="n">
-        <v>2.941176525586755</v>
+        <v>1.802325634692455</v>
       </c>
       <c r="J96" t="n">
         <v>-2</v>
@@ -4956,11 +4956,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.47</v>
+        <v>0.06</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4979,19 +4979,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.429999828338623</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="I97" t="n">
-        <v>6.325706741033583</v>
+        <v>0.8823529164271378</v>
       </c>
       <c r="J97" t="n">
         <v>-2</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>50.59999847412109</v>
+        <v>34.63999938964844</v>
       </c>
       <c r="I98" t="n">
-        <v>2.766798502407104</v>
+        <v>1.010392627502734</v>
       </c>
       <c r="J98" t="n">
         <v>-2</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.3</v>
+        <v>0.5543</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3.457000017166138</v>
+        <v>6.840000152587891</v>
       </c>
       <c r="I99" t="n">
-        <v>8.678044504203498</v>
+        <v>8.103800988809665</v>
       </c>
       <c r="J99" t="n">
         <v>-2</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>13.14999961853027</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I100" t="n">
-        <v>0.9125475549892977</v>
+        <v>2.690582936628342</v>
       </c>
       <c r="J100" t="n">
         <v>-2</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3.599999904632568</v>
+        <v>12.75</v>
       </c>
       <c r="I101" t="n">
-        <v>4.722222347318394</v>
+        <v>1.568627450980392</v>
       </c>
       <c r="J101" t="n">
         <v>-2</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7</v>
+        <v>0.103</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>22.10000038146973</v>
+        <v>6.809999942779541</v>
       </c>
       <c r="I102" t="n">
-        <v>3.167420759806555</v>
+        <v>1.512481657348736</v>
       </c>
       <c r="J102" t="n">
         <v>-2</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.035</v>
+        <v>0.19</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2.400000095367432</v>
+        <v>5.692999839782715</v>
       </c>
       <c r="I103" t="n">
-        <v>1.458333275384376</v>
+        <v>3.337432027878851</v>
       </c>
       <c r="J103" t="n">
         <v>-2</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.33</v>
+        <v>0.432</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.639999866485596</v>
+        <v>10.0600004196167</v>
       </c>
       <c r="I104" t="n">
-        <v>5.851063968298106</v>
+        <v>4.294234413326793</v>
       </c>
       <c r="J104" t="n">
         <v>-2</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.8820000290870667</v>
+        <v>25.55999946594238</v>
       </c>
       <c r="I105" t="n">
-        <v>7.936507674773551</v>
+        <v>1.721439785576997</v>
       </c>
       <c r="J105" t="n">
         <v>-2</v>
@@ -5379,11 +5379,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.71</v>
+        <v>0.03</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>50.75</v>
+        <v>1.019999980926514</v>
       </c>
       <c r="I106" t="n">
-        <v>1.399014778325123</v>
+        <v>2.941176525586755</v>
       </c>
       <c r="J106" t="n">
         <v>-2</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.35</v>
+        <v>0.47</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>102.5</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I107" t="n">
-        <v>1.317073170731707</v>
+        <v>6.308724993730711</v>
       </c>
       <c r="J107" t="n">
         <v>-2</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.28000020980835</v>
+        <v>50.97999954223633</v>
       </c>
       <c r="I108" t="n">
-        <v>1.098901067230959</v>
+        <v>2.74617499523537</v>
       </c>
       <c r="J108" t="n">
         <v>-2</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>260</v>
+        <v>3.414999961853027</v>
       </c>
       <c r="I109" t="n">
-        <v>1.153846153846154</v>
+        <v>8.784773158158858</v>
       </c>
       <c r="J109" t="n">
         <v>-2</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>4.434000015258789</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="I110" t="n">
-        <v>3.834009910125767</v>
+        <v>0.8823529164271378</v>
       </c>
       <c r="J110" t="n">
         <v>-2</v>
@@ -5614,11 +5614,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.297</v>
+        <v>0.17</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>7.449999809265137</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I111" t="n">
-        <v>3.986577283272386</v>
+        <v>4.941860382914093</v>
       </c>
       <c r="J111" t="n">
         <v>-2</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>56.90000152587891</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7908611387212947</v>
+        <v>3.160270934787706</v>
       </c>
       <c r="J112" t="n">
         <v>-2</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>5.679999828338623</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I113" t="n">
-        <v>0.704225373395827</v>
+        <v>1.495726550589419</v>
       </c>
       <c r="J113" t="n">
         <v>-2</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.05</v>
+        <v>0.33</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>36.43999862670898</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="I114" t="n">
-        <v>2.881449065781233</v>
+        <v>5.77933446226548</v>
       </c>
       <c r="J114" t="n">
         <v>-2</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0005621070</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1.450000047683716</v>
+        <v>0.8939999938011169</v>
       </c>
       <c r="I115" t="n">
-        <v>3.44827574867131</v>
+        <v>7.829977682927423</v>
       </c>
       <c r="J115" t="n">
         <v>-2</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>20.86000061035156</v>
+        <v>50.75</v>
       </c>
       <c r="I116" t="n">
-        <v>1.821668211320324</v>
+        <v>1.399014778325123</v>
       </c>
       <c r="J116" t="n">
         <v>-2</v>
@@ -5896,15 +5896,15 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5924,14 +5924,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>26.48999977111816</v>
+        <v>103.5</v>
       </c>
       <c r="I117" t="n">
-        <v>2.26500568208451</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="J117" t="n">
         <v>-2</v>
@@ -5943,11 +5943,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>34.59999847412109</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I118" t="n">
-        <v>1.011560738252</v>
+        <v>1.126760578514967</v>
       </c>
       <c r="J118" t="n">
         <v>-2</v>
@@ -5990,11 +5990,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.017</v>
+        <v>3</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6018,14 +6018,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.299999952316284</v>
+        <v>260</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5151515225952542</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="J119" t="n">
         <v>-2</v>
@@ -6037,11 +6037,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2.710000038146973</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3690036848426667</v>
+        <v>3.890160284941308</v>
       </c>
       <c r="J120" t="n">
         <v>-2</v>
@@ -6084,11 +6084,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.12</v>
+        <v>0.297</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>21.19000053405762</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I121" t="n">
-        <v>5.285511900766028</v>
+        <v>3.986577283272386</v>
       </c>
       <c r="J121" t="n">
         <v>-2</v>
@@ -6131,11 +6131,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6159,14 +6159,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1.480000019073486</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="I122" t="n">
-        <v>6.756756669679118</v>
+        <v>0.7867132762200246</v>
       </c>
       <c r="J122" t="n">
         <v>-2</v>
@@ -6178,11 +6178,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>8.739999771118164</v>
+        <v>5.5</v>
       </c>
       <c r="I123" t="n">
-        <v>2.974828453190412</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J123" t="n">
         <v>-2</v>
@@ -6225,11 +6225,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6253,14 +6253,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.226000070571899</v>
+        <v>37.29999923706055</v>
       </c>
       <c r="I124" t="n">
-        <v>4.14645090178665</v>
+        <v>2.815013462404419</v>
       </c>
       <c r="J124" t="n">
         <v>-2</v>
@@ -6272,11 +6272,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6300,30 +6300,30 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>8.819999694824219</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I125" t="n">
-        <v>3.968254105557261</v>
+        <v>3.44827574867131</v>
       </c>
       <c r="J125" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K125" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.096</v>
+        <v>0.38</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6347,44 +6347,44 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>5.300000190734863</v>
+        <v>20.73999977111816</v>
       </c>
       <c r="I126" t="n">
-        <v>1.811320689531697</v>
+        <v>1.832208313373153</v>
       </c>
       <c r="J126" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K126" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6394,30 +6394,30 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>6.150000095367432</v>
+        <v>26.19000053405762</v>
       </c>
       <c r="I127" t="n">
-        <v>4.878048704844394</v>
+        <v>2.290950697842701</v>
       </c>
       <c r="J127" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K127" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6441,30 +6441,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>11.5</v>
+        <v>35.54999923706055</v>
       </c>
       <c r="I128" t="n">
-        <v>1.739130434782609</v>
+        <v>0.984528853759097</v>
       </c>
       <c r="J128" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K128" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.06</v>
+        <v>0.017</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6473,45 +6473,45 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.199999809265137</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.5151515225952542</v>
       </c>
       <c r="J129" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K129" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6535,30 +6535,30 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>18.70000076293945</v>
+        <v>2.704999923706055</v>
       </c>
       <c r="I130" t="n">
-        <v>2.673796682355883</v>
+        <v>0.3696857775248749</v>
       </c>
       <c r="J130" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K130" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.06</v>
+        <v>1.12</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6567,12 +6567,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6582,30 +6582,30 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.200000047683716</v>
+        <v>21.54999923706055</v>
       </c>
       <c r="I131" t="n">
-        <v>2.727272668160684</v>
+        <v>5.197215961260376</v>
       </c>
       <c r="J131" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K131" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6629,30 +6629,30 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="I132" t="n">
-        <v>3.333333333333333</v>
+        <v>6.756756669679118</v>
       </c>
       <c r="J132" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K132" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6676,30 +6676,30 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>3.579999923706055</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I133" t="n">
-        <v>2.79329614891385</v>
+        <v>2.869757041479252</v>
       </c>
       <c r="J133" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K133" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.11</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6708,12 +6708,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6723,30 +6723,30 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>3.579999923706055</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I134" t="n">
-        <v>3.072625763805235</v>
+        <v>4.139013417513266</v>
       </c>
       <c r="J134" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="K134" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>9.149999618530273</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9289617873629289</v>
+        <v>3.914988998075476</v>
       </c>
       <c r="J135" t="n">
         <v>-9</v>
@@ -6789,11 +6789,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.095</v>
+        <v>0.096</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>4.800000190734863</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I136" t="n">
-        <v>1.979166588021652</v>
+        <v>1.811320689531697</v>
       </c>
       <c r="J136" t="n">
         <v>-9</v>
@@ -6836,11 +6836,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1.179999947547913</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I137" t="n">
-        <v>2.542372994366755</v>
+        <v>4.878048704844394</v>
       </c>
       <c r="J137" t="n">
         <v>-9</v>
@@ -6883,11 +6883,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>8.100000381469727</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I138" t="n">
-        <v>1.111111058783305</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J138" t="n">
         <v>-9</v>
@@ -6930,11 +6930,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6953,19 +6953,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>8.399999618530273</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I139" t="n">
-        <v>1.190476244539363</v>
+        <v>0.6535947495140209</v>
       </c>
       <c r="J139" t="n">
         <v>-9</v>
@@ -6977,11 +6977,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7005,14 +7005,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>6.920000076293945</v>
+        <v>18.78000068664551</v>
       </c>
       <c r="I140" t="n">
-        <v>3.179190716394075</v>
+        <v>2.662406718416953</v>
       </c>
       <c r="J140" t="n">
         <v>-9</v>
@@ -7024,11 +7024,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.61</v>
+        <v>0.06</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7052,30 +7052,30 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>27.04999923706055</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I141" t="n">
-        <v>2.255083242901736</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J141" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K141" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7099,30 +7099,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2.740000009536743</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>5.474452535690348</v>
+        <v>3.259452379572819</v>
       </c>
       <c r="J142" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K142" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>11.39999961853027</v>
+        <v>3.619999885559082</v>
       </c>
       <c r="I143" t="n">
-        <v>6.140351082662987</v>
+        <v>2.762431026556669</v>
       </c>
       <c r="J143" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K143" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5105</v>
+        <v>0.11</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,44 +7193,44 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>8.680000305175781</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="I144" t="n">
-        <v>5.881336198750994</v>
+        <v>3.081232550614696</v>
       </c>
       <c r="J144" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K144" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.27</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7240,30 +7240,30 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0005545238</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>8.524999618530273</v>
+        <v>9.149999618530273</v>
       </c>
       <c r="I145" t="n">
-        <v>3.167155566941228</v>
+        <v>0.9289617873629289</v>
       </c>
       <c r="J145" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K145" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.35</v>
+        <v>0.095</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7272,12 +7272,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7287,30 +7287,30 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>6.735000133514404</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I146" t="n">
-        <v>5.196733378791571</v>
+        <v>1.946721265822835</v>
       </c>
       <c r="J146" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K146" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.1</v>
+        <v>0.03</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7334,30 +7334,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>41.79999923706055</v>
+        <v>1.200000047683716</v>
       </c>
       <c r="I147" t="n">
-        <v>2.631578995400369</v>
+        <v>2.49999990065893</v>
       </c>
       <c r="J147" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K147" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.75</v>
+        <v>0.09</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7366,45 +7366,45 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>16.89999961853027</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I148" t="n">
-        <v>4.437869922657575</v>
+        <v>1.097561001139408</v>
       </c>
       <c r="J148" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K148" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7428,30 +7428,30 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>10.05000019073486</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I149" t="n">
-        <v>4.27860688397219</v>
+        <v>1.190476244539363</v>
       </c>
       <c r="J149" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K149" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7475,30 +7475,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>4.224999904632568</v>
+        <v>7.090000152587891</v>
       </c>
       <c r="I150" t="n">
-        <v>3.55029593812606</v>
+        <v>3.102961851414047</v>
       </c>
       <c r="J150" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K150" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.197169</v>
+        <v>0.61</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7522,14 +7522,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>11.72000026702881</v>
+        <v>26.89999961853027</v>
       </c>
       <c r="I151" t="n">
-        <v>1.682329313205598</v>
+        <v>2.267658024722784</v>
       </c>
       <c r="J151" t="n">
         <v>-16</v>
@@ -7541,11 +7541,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1.1</v>
+        <v>0.15</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>28.75</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="I152" t="n">
-        <v>3.82608695652174</v>
+        <v>5.357142948374458</v>
       </c>
       <c r="J152" t="n">
         <v>-16</v>
@@ -7588,11 +7588,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7616,14 +7616,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>66.09999847412109</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7110438893338407</v>
+        <v>6.034482560174792</v>
       </c>
       <c r="J153" t="n">
         <v>-16</v>
@@ -7635,11 +7635,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.2</v>
+        <v>0.5105</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>86.69999694824219</v>
+        <v>8.779999732971191</v>
       </c>
       <c r="I154" t="n">
-        <v>1.384083093701112</v>
+        <v>5.814350974100138</v>
       </c>
       <c r="J154" t="n">
         <v>-16</v>
@@ -7682,7 +7682,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7710,14 +7710,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>22.25</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="I155" t="n">
-        <v>1.213483146067416</v>
+        <v>3.165299043988984</v>
       </c>
       <c r="J155" t="n">
         <v>-16</v>
@@ -7729,11 +7729,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -7757,14 +7757,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>10.25</v>
+        <v>6.735000133514404</v>
       </c>
       <c r="I156" t="n">
-        <v>3.707317073170731</v>
+        <v>5.196733378791571</v>
       </c>
       <c r="J156" t="n">
         <v>-16</v>
@@ -7776,11 +7776,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7804,14 +7804,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>32.5</v>
+        <v>41.59999847412109</v>
       </c>
       <c r="I157" t="n">
-        <v>0.923076923076923</v>
+        <v>2.64423086622058</v>
       </c>
       <c r="J157" t="n">
         <v>-16</v>
@@ -7823,11 +7823,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.007</v>
+        <v>0.75</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7836,45 +7836,45 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IT0001073045</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0.1689999997615814</v>
+        <v>16.85000038146973</v>
       </c>
       <c r="I158" t="n">
-        <v>4.142011840162914</v>
+        <v>4.451038474899915</v>
       </c>
       <c r="J158" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="K158" t="n">
-        <v>-21</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7883,12 +7883,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7898,30 +7898,30 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>6.550000190734863</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="I159" t="n">
-        <v>2.442748020470655</v>
+        <v>4.114832610989668</v>
       </c>
       <c r="J159" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="K159" t="n">
-        <v>-21</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.065</v>
+        <v>0.15</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7945,30 +7945,30 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>2.025000095367432</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="I160" t="n">
-        <v>3.209876392040658</v>
+        <v>3.488371938289734</v>
       </c>
       <c r="J160" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="K160" t="n">
-        <v>-21</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.25</v>
+        <v>0.197169</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7977,12 +7977,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7992,30 +7992,30 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>8.020000457763672</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I161" t="n">
-        <v>3.117206804620445</v>
+        <v>1.670923701804796</v>
       </c>
       <c r="J161" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="K161" t="n">
-        <v>-21</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8039,30 +8039,30 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>IT0005549255</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1.299999952316284</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="I162" t="n">
-        <v>5.384615582121908</v>
+        <v>3.780068678969699</v>
       </c>
       <c r="J162" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="K162" t="n">
-        <v>-21</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8071,12 +8071,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8086,30 +8086,30 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.070000171661377</v>
+        <v>67.5</v>
       </c>
       <c r="I163" t="n">
-        <v>7.072135613293843</v>
+        <v>0.6962962962962962</v>
       </c>
       <c r="J163" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="K163" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.65</v>
+        <v>1.2</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8118,12 +8118,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -8133,30 +8133,30 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>IT0004776628</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>19.22999954223633</v>
+        <v>88</v>
       </c>
       <c r="I164" t="n">
-        <v>3.380135285871198</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="J164" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="K164" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8180,30 +8180,30 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>12.88000011444092</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I165" t="n">
-        <v>4.192546546599466</v>
+        <v>1.184210565942147</v>
       </c>
       <c r="J165" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="K165" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -8212,12 +8212,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8227,30 +8227,30 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>5.498000144958496</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I166" t="n">
-        <v>1.818843167759773</v>
+        <v>3.671497449220761</v>
       </c>
       <c r="J166" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="K166" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -8259,12 +8259,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8274,30 +8274,30 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>8.319999694824219</v>
+        <v>33.09999847412109</v>
       </c>
       <c r="I167" t="n">
-        <v>1.923076993614967</v>
+        <v>0.9063444526577609</v>
       </c>
       <c r="J167" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="K167" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>3.615</v>
+        <v>0.007</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8321,30 +8321,30 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>NL0011585146</t>
+          <t>IT0001073045</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>286.1499938964844</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="I168" t="n">
-        <v>1.263323458712964</v>
+        <v>4.117647015512197</v>
       </c>
       <c r="J168" t="n">
-        <v>-30</v>
+        <v>-23</v>
       </c>
       <c r="K168" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1.36</v>
+        <v>0.16</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8368,30 +8368,30 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>IT0005144784</t>
+          <t>IT0001033700</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>27.79999923706055</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="I169" t="n">
-        <v>4.892086465193014</v>
+        <v>2.342606175509029</v>
       </c>
       <c r="J169" t="n">
-        <v>-30</v>
+        <v>-23</v>
       </c>
       <c r="K169" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>5.8216</v>
+        <v>0.065</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -8400,45 +8400,45 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>NL0015000LU4</t>
+          <t>IT0003372205</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>13.90999984741211</v>
+        <v>2.019999980926514</v>
       </c>
       <c r="I170" t="n">
-        <v>41.85190556334249</v>
+        <v>3.217821812561921</v>
       </c>
       <c r="J170" t="n">
-        <v>-30</v>
+        <v>-23</v>
       </c>
       <c r="K170" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.585</v>
+        <v>0.25</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -8447,12 +8447,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8462,30 +8462,30 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>IT0004931058</t>
+          <t>IT0003365613</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>14.30000019073486</v>
+        <v>8.409999847412109</v>
       </c>
       <c r="I171" t="n">
-        <v>4.090909036344128</v>
+        <v>2.972651659166545</v>
       </c>
       <c r="J171" t="n">
-        <v>-30</v>
+        <v>-23</v>
       </c>
       <c r="K171" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.63</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -8494,12 +8494,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8509,30 +8509,30 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>IT0000062957</t>
+          <t>IT0005549255</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>20.6200008392334</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="I172" t="n">
-        <v>3.055286005620851</v>
+        <v>5.384615582121908</v>
       </c>
       <c r="J172" t="n">
-        <v>-30</v>
+        <v>-23</v>
       </c>
       <c r="K172" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -8556,14 +8556,14 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>IT0004176001</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>142.8999938964844</v>
+        <v>7.130000114440918</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6298110835833575</v>
+        <v>7.012622608340678</v>
       </c>
       <c r="J173" t="n">
         <v>-30</v>
@@ -8575,11 +8575,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1.7208</v>
+        <v>0.65</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -8603,19 +8603,489 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>IT0005239360</t>
+          <t>IT0004776628</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>70.43000030517578</v>
+        <v>19.4950008392334</v>
       </c>
       <c r="I174" t="n">
-        <v>2.443277002049852</v>
+        <v>3.334188109866016</v>
       </c>
       <c r="J174" t="n">
         <v>-30</v>
       </c>
       <c r="K174" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Banco BPM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>IT0005218380</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>13.19999980926514</v>
+      </c>
+      <c r="I175" t="n">
+        <v>4.090909150021137</v>
+      </c>
+      <c r="J175" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K175" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>NL0015435975</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>5.535999774932861</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1.806358454940739</v>
+      </c>
+      <c r="J176" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>IT0005215329</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>8.439999580383301</v>
+      </c>
+      <c r="I177" t="n">
+        <v>1.895734691407812</v>
+      </c>
+      <c r="J177" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>NL0011585146</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>290.25</v>
+      </c>
+      <c r="I178" t="n">
+        <v>1.245478036175711</v>
+      </c>
+      <c r="J178" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K178" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>IT0005144784</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>27.39999961853027</v>
+      </c>
+      <c r="I179" t="n">
+        <v>4.96350371873819</v>
+      </c>
+      <c r="J179" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Iveco Group N.V.</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>5.8216</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Straordinario</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>NL0015000LU4</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>13.90999984741211</v>
+      </c>
+      <c r="I180" t="n">
+        <v>41.85190556334249</v>
+      </c>
+      <c r="J180" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>IT0004931058</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>14.64999961853027</v>
+      </c>
+      <c r="I181" t="n">
+        <v>3.993174165411267</v>
+      </c>
+      <c r="J181" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K181" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>IT0000062957</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>20.80999946594238</v>
+      </c>
+      <c r="I182" t="n">
+        <v>3.027390755252335</v>
+      </c>
+      <c r="J182" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>IT0004176001</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>144.3999938964844</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.6232687244053352</v>
+      </c>
+      <c r="J183" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K183" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1.7208</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>IT0005239360</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>72.26999664306641</v>
+      </c>
+      <c r="I184" t="n">
+        <v>2.381071094411202</v>
+      </c>
+      <c r="J184" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K184" t="n">
         <v>-28</v>
       </c>
     </row>
@@ -8630,7 +9100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9656,7 +10126,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9690,7 +10160,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9700,14 +10170,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9717,14 +10187,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9734,14 +10204,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9751,14 +10221,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9768,14 +10238,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9785,14 +10255,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9809,7 +10279,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9826,7 +10296,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9843,7 +10313,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9860,7 +10330,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9870,14 +10340,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9894,7 +10364,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9904,14 +10374,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9928,7 +10398,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9938,14 +10408,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9962,7 +10432,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9972,14 +10442,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9996,7 +10466,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10006,14 +10476,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10047,7 +10517,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10081,7 +10551,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10098,7 +10568,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10149,7 +10619,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10159,14 +10629,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10176,14 +10646,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10193,14 +10663,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10210,7 +10680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10721,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10261,14 +10731,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10285,7 +10755,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10295,14 +10765,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10455,7 +10925,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10472,7 +10942,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10489,7 +10959,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10515,6 +10985,176 @@
         </is>
       </c>
       <c r="C111" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PIQUADRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PROMOTICA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>RISANAMENTO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>RISANAMENTO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>VNE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>BFF Bank S.P.A.</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Gas Plus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Iveco Group N.V.</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>OVS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Simone S.p.A.</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -10544,7 +11184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10567,49 +11207,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
